--- a/_tooling/CABRU_testi_IT_da_correggere.xlsx
+++ b/_tooling/CABRU_testi_IT_da_correggere.xlsx
@@ -1,45 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Istruzioni" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Home" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Prodotti (hub categorie)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Prod_Anticorpi" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Prod_Molecole biochimiche" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Prod_Kit ELISA" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Prod_Proteine" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Prod_Acidi nucleici" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Prod_Elettroforesi WB" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Prod_Terreni microbiologia" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Prod_Soluzioni e polveri" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Prod_Plasmi" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Le aziende che rappresentiamo" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Az_Cayman Chemical" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Az_A&amp;A Biotechnology" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Az_Affinity Biologicals" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Az_Bioatlas" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Az_BioMedica Diagnostics" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Az_BioVendor" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Az_Candor Medix Biochemica" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Az_Condalab" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Az_Enzyme Research Laboratories" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Az_ExBio" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Az_FineTest" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Az_G Biosciences" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Az_LDN — Labor Diagnostika Nord" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Az_MAGBIO" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Az_ReliaTech" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Az_Rovalab" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Az_SEQENS" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="Guida_Eicosanoidi" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="App_Tossicologia forense" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="Catalogo (intro)" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istruzioni" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prodotti (hub categorie)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prod_Anticorpi" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prod_Molecole biochimiche" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prod_Kit ELISA" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prod_Proteine" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prod_Acidi nucleici" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prod_Elettroforesi WB" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prod_Terreni microbiologia" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prod_Soluzioni e polveri" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prod_Plasmi" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Le aziende che rappresentiamo" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Az_Cayman Chemical" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Az_A&amp;A Biotechnology" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Az_Affinity Biologicals" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Az_Bioatlas" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Az_BioMedica Diagnostics" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Az_BioVendor" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Az_Candor Medix Biochemica" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Az_Condalab" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Az_Enzyme Research Laboratories" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Az_ExBio" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Az_FineTest" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Az_G Biosciences" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Az_LDN — Labor Diagnostika Nord" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Az_MAGBIO" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Az_ReliaTech" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Az_Rovalab" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Az_SEQENS" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guida_Eicosanoidi" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App_Tossicologia forense" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo (intro)" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -878,7 +878,7 @@
       </c>
       <c r="C18" s="9" t="inlineStr"/>
     </row>
-    <row r="19" ht="21" customHeight="1">
+    <row r="19" ht="36" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
@@ -886,7 +886,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Sì, l'intera gamma tramite Condalab. Il dettaglio è riportato nella pagina Condalab .</t>
+          <t>Sì, tutti questi prodotti sono presenti nel paniere CABRU. Il dettaglio è riportato nella pagina Condalab .</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr"/>
@@ -912,7 +912,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Coprono più ambiti; la referenza adatta al campo d'uso viene individuata in fase di richiesta.</t>
+          <t>Coprono più ambiti;</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr"/>
@@ -993,7 +993,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Soluzioni pronte all'uso, buffer stabilizzanti, BSA e polveri per la preparazione in laboratorio, dai produttori rappresentati da CABRU in Italia.</t>
+          <t>Soluzioni pronte all'uso, tamponi stabilizzanti, BSA e polveri per la preparazione in laboratorio di tamponi.</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Cayman Chemical Italia — 67.119 referenze distribuite da CABRU</t>
+          <t>Cayman Chemical - molecole biochimiche, anticorpi, kit</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr"/>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>CABRU distribuisce Cayman Chemical in Italia: 67.119 referenze fra molecole biochimiche, standard deuterati, kit ELISA, anticorpi e proteine.</t>
+          <t>CABRU fornisce i prodotti di Cayman Chemical: molecole biochimiche, inibitori, kit, anticorpi, proteine, standard analitici</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr"/>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr"/>
     </row>
-    <row r="10" ht="81" customHeight="1">
+    <row r="10" ht="111" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Testo</t>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Cayman sviluppa e produce internamente piccole molecole biochimiche, saggi immunoenzimatici e reagenti ad elevata purezza. La sintesi dei mediatori lipidici è l'area storica dell'azienda e si riflette nel catalogo distribuito in Italia: 1.136 referenze di prostaglandine, 167 di leucotrieni, 114 di sfingosine, 94 di resolvine e 33 di lipossine. I prodotti Cayman sono destinati alla ricerca (Research Use Only).</t>
+          <t>Cayman sviluppa e produce internamente piccole molecole biochimiche, saggi immunoenzimatici e reagenti ad elevata purezza. La sintesi dei mediatori lipidici è l'area storica dell'azienda e si riflette nel catalogo distribuito in Italia: 1.136 referenze di prostaglandine, 167 di leucotrieni, 114 di sfingosine, 94 di resolvine e 33 di lipossine. I prodotti Cayman Chemical sono destinati esclusivamente ad uso ricerca e per controllo qualità. Non possono essere utilizzati per la formulazione di preparati farmaceutici, galenici, cosmetici, integratori, destinati a uomo o animale.</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr"/>
@@ -1929,85 +1929,85 @@
       </c>
       <c r="C17" s="9" t="inlineStr"/>
     </row>
-    <row r="18" ht="21" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Titolo sezione</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
+    <row r="18" ht="51" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Tutti i prodotti presenti nel paniere Cayman Chemical tranne i prodotti tabellati (stupefacenti) anche in versione CRM, tossine, prodotti classificati come pericolosi e alcuni prodotti la cui commercializzazione è limitata solo agli USA.</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr"/>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Titolo sezione</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Formati e quantità</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr"/>
-    </row>
-    <row r="19" ht="81" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Testo</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20" ht="81" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Il catalogo è organizzato per taglio: 51.918 referenze sono espresse in milligrammi, 6.118 in microgrammi e 5.759 in grammi, su 265 formati distinti. I ricorrenti sono 5 mg con 11.974 referenze, 10 mg con 10.879, 1 mg con 10.702 e 25 mg con 7.260. Lo stesso composto è quindi spesso ordinabile in più quantità, e la scelta del taglio incide sul prezzo unitario più di quanto si presuma.</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr"/>
-    </row>
-    <row r="20" ht="21" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Titolo sezione</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Titolo sezione</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Aree di ricerca coperte</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr"/>
-    </row>
-    <row r="21" ht="66" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Testo</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Oncologia, neuroscienze, infiammazione ed immunologia, metabolismo e biologia lipidica, stress ossidativo ed epigenetica. A queste si aggiunge la tossicologia analitica e forense, dove trovano impiego i composti di riferimento ed i marcati isotopicamente. → Metabolismo e lipidi · Endocannabinoidi · Tossicologia e scienze forensi</t>
-        </is>
-      </c>
       <c r="C21" s="9" t="inlineStr"/>
     </row>
-    <row r="22" ht="21" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Titolo sezione</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
+    <row r="22" ht="81" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Oncologia, neuroscienze, infiammazione ed immunologia, patologie cardiovascolari, trasduzione del segnale, biologia della cellula, apoptosi, ciclo cellulare, danni al DNA, metabolismo lipidi e zuccheri, lipidomica, metabolomica, stress ossidativo, epigenetica, tossicologia, farmacologia, nanoparticelle, endocrinologia, infezione, biologia delle piante. → Metabolismo e lipidi · Endocannabinoidi · Tossicologia e scienze forensi</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Titolo sezione</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Come si ordina Cayman Chemical in Italia</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr"/>
-    </row>
-    <row r="23" ht="66" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Testo</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>CABRU raccoglie la richiesta, verifica la disponibilità presso il produttore, formula il preventivo e segue l'ordine sino alla consegna, con assistenza tecnica in lingua italiana. Non è necessario alcun rapporto diretto con gli Stati Uniti: comunicazione con il produttore, documentazione e logistica restano in carico a CABRU.</t>
-        </is>
-      </c>
       <c r="C23" s="9" t="inlineStr"/>
     </row>
-    <row r="24" ht="66" customHeight="1">
+    <row r="24" ht="81" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Testo</t>
@@ -2015,20 +2015,20 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Su un catalogo di questa dimensione la ricerca per codice resta la via più rapida, perché 67.119 referenze non stanno in un menu di navigazione. Chi non dispone del codice può indicare il nome della molecola, il numero CAS o l'applicazione analitica: CABRU risale alla referenza corrispondente ed ai formati disponibili. → Consulta il catalogo · Richiedi un preventivo</t>
+          <t>CABRU è fornitore autorizzato e diretto di Cayman Chemical per l'Italia pertanto richieste di preventivi, informazioni tecnico-scientifiche, gestione degli ordini diretti o mediante MePA, consegna dei prodotti, risoluzione di eventuali problematiche vengono svolte direttamente da CABRU. L'acquisto avviene trasmettendo a CABRU un buono d'ordine rilasciato dall'amministrazione dell'ente o dall'azienda a cui si afferisce.</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr"/>
     </row>
-    <row r="25" ht="21" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Titolo sezione</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Domande frequenti</t>
+    <row r="25" ht="66" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Su un catalogo di questa dimensione la ricerca per codice resta la via più rapida, perché 67.119 referenze non stanno in un menu di navigazione. Per l'individuazione del prodotto desiderato e/o la richiesta di un preventivo è sufficiente mandare un'email a: info@cabru.it. → Consulta il catalogo · Richiedi un preventivo</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr"/>
@@ -2036,158 +2036,171 @@
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
+          <t>Titolo sezione</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Domande frequenti</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27" ht="21" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
           <t>FAQ — Domanda</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Chi distribuisce Cayman Chemical in Italia?</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr"/>
-    </row>
-    <row r="27" ht="51" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>CABRU s.a.s. distribuisce Cayman Chemical in Italia. Ha sede ad Arcore (MB) e cura richieste tecniche, preventivi, ordini ed assistenza in lingua italiana sulle 67.119 referenze del catalogo.</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr"/>
-    </row>
-    <row r="28" ht="21" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>CABRU s.a.s. è fornitore autorizzato e diretto di Cayman Chemical in Italia e ne gestisce richieste, preventivi ed ordini con assistenza tecnica in lingua italiana.</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>FAQ — Domanda</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Quante referenze Cayman Chemical sono ordinabili tramite CABRU?</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr"/>
-    </row>
-    <row r="29" ht="51" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr"/>
+    </row>
+    <row r="30" ht="51" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>67.119 referenze, corrispondenti a 23.429 prodotti distinti proposti in più formati. Le categorie più ampie sono le piccole molecole biochimiche, con 60.791 referenze, e gli standard analitici marcati, con 3.153.</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr"/>
-    </row>
-    <row r="30" ht="21" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr"/>
+    </row>
+    <row r="31" ht="21" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>FAQ — Domanda</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>Cayman Chemical fornisce standard marcati per spettrometria di massa?</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr"/>
-    </row>
-    <row r="31" ht="51" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr"/>
+    </row>
+    <row r="32" ht="51" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Sì. Il catalogo distribuito in Italia comprende 3.153 referenze di composti marcati, fra cui 1.341 molecole deuterate distinte, tipicamente impiegate come standard interni nei dosaggi in spettrometria di massa. → Tossicologia e scienze forensi</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr"/>
-    </row>
-    <row r="32" ht="21" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr"/>
+    </row>
+    <row r="33" ht="21" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>FAQ — Domanda</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>Cosa sono gli eicosanoidi e perché Cayman ne è un riferimento?</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr"/>
-    </row>
-    <row r="33" ht="51" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Cosa sono le LNP?</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Gli eicosanoidi sono mediatori lipidici coinvolti in infiammazione e segnalazione cellulare. Cayman li sintetizza dal 1980: nel catalogo distribuito in Italia figurano 1.136 referenze di prostaglandine, 167 di leucotrieni, 94 di resolvine e 33 di lipossine. → Metabolismo e lipidi</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr"/>
-    </row>
-    <row r="34" ht="21" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Le LNP sono nanoparticelle lipidiche utilizzate come vettori di mRNA. Cayman Chemical offre una vasta gamma di opportunità. → Metabolismo e lipidi</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr"/>
+    </row>
+    <row r="35" ht="21" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>FAQ — Domanda</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>In quali formati si ordinano i prodotti Cayman Chemical?</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr"/>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Su 265 tagli distinti. I più ricorrenti sono 5 mg con 11.974 referenze, 10 mg con 10.879, 1 mg con 10.702 e 25 mg con 7.260. Lo stesso composto è spesso ordinabile in più quantità.</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr"/>
-    </row>
-    <row r="36" ht="21" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr"/>
+    </row>
+    <row r="37" ht="21" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>FAQ — Domanda</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>CABRU è distributore esclusivo di Cayman Chemical?</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr"/>
-    </row>
-    <row r="37" ht="21" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38" ht="21" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>No. CABRU distribuisce Cayman Chemical in Italia su base non esclusiva.</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr"/>
+      <c r="C38" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2205,7 +2218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2395,92 +2408,92 @@
       <c r="C15" s="9" t="inlineStr"/>
     </row>
     <row r="16" ht="21" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Titolo sezione</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>I prodotti garantiscono buone rese, eccellente purezza, elevata riproducibilità e sensibilità.</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Titolo sezione</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Aree di applicazione</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr"/>
-    </row>
-    <row r="17" ht="81" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Testo</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr"/>
+    </row>
+    <row r="18" ht="81" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Le referenze A&amp;A trovano impiego nella genotipizzazione, negli studi di espressione genica, nella preparazione dei campioni per sequenziamento Sanger e NGS e nella microbiologia molecolare. Il produttore indica fra i propri utilizzatori laboratori universitari e di ricerca, laboratori veterinari, strutture sanitarie e laboratori ambientali e forensi: una gamma pensata più per la varietà di matrici che per il singolo protocollo.</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr"/>
-    </row>
-    <row r="18" ht="21" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Titolo sezione</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr"/>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Titolo sezione</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Le referenze A&amp;A Biotechnology nel catalogo CABRU</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr"/>
-    </row>
-    <row r="19" ht="81" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Testo</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20" ht="81" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Le 337 referenze A&amp;A presenti nel catalogo CABRU ricadono tutte nell'area della biologia molecolare. Le famiglie più rappresentate sono i kit per DNA genomico (45 referenze), i kit per RNA e microRNA (46), la linea MagnifiQ a biglie magnetiche (49) e i kit per DNA plasmidico (15). Ogni voce riporta codice, denominazione e formato: la ricerca può partire dal codice oppure dal nome del kit.</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr"/>
-    </row>
-    <row r="20" ht="21" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Titolo sezione</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Titolo sezione</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Come CABRU segue A&amp;A Biotechnology</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr"/>
-    </row>
-    <row r="21" ht="81" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Testo</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Sui kit di estrazione la referenza giusta dipende quasi sempre da due sole variabili: la matrice di partenza e ciò che si deve fare a valle. CABRU parte da lì — tipo di campione, volume, applicazione successiva — e indica il kit coerente, verificando presso il produttore i formati e le taglie che non figurano a catalogo. CABRU distribuisce A&amp;A Biotechnology in Italia in regime non esclusivo. → Richiedi informazioni e preventivo</t>
-        </is>
-      </c>
       <c r="C21" s="9" t="inlineStr"/>
     </row>
-    <row r="22" ht="21" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Titolo sezione</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Domande frequenti</t>
+    <row r="22" ht="96" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Sui kit di estrazione la referenza giusta dipende quasi sempre da due sole variabili: la matrice di partenza e ciò che si deve fare a valle. CABRU parte da lì — tipo di campione, volume, applicazione successiva — e indica il kit coerente. CABRU rappresenta A&amp;A Biotechnology in Italia offrendo informazioni tecniche, preventivi competitivi e gestione dell'ordine fino alla consegna. CABRU distribuisce A&amp;A Biotechnology in Italia in regime non esclusivo. È sufficiente contattare CABRU a info@cabru.it. → Richiedi informazioni e preventivo</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr"/>
@@ -2488,132 +2501,145 @@
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
+          <t>Titolo sezione</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Domande frequenti</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr"/>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
           <t>FAQ — Domanda</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Chi distribuisce A&amp;A Biotechnology in Italia?</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr"/>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>CABRU distribuisce A&amp;A Biotechnology in Italia e ne gestisce richieste tecniche, preventivi e ordini come referente locale.</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr"/>
-    </row>
-    <row r="25" ht="21" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr"/>
+    </row>
+    <row r="26" ht="21" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>FAQ — Domanda</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Quante referenze A&amp;A Biotechnology sono presenti nel catalogo CABRU?</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr"/>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>337, tutte nell'area della biologia molecolare: estrazione e purificazione di acidi nucleici, PCR, retrotrascrizione ed elettroforesi.</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr"/>
-    </row>
-    <row r="27" ht="21" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28" ht="21" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>FAQ — Domanda</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Che cos'è la linea MagnifiQ?</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr"/>
-    </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>È la piattaforma A&amp;A a biglie magnetiche per l'estrazione di acidi nucleici, adatta ai protocolli automatizzati e al clean-up per NGS. Nel catalogo CABRU figurano 49 referenze MagnifiQ.</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr"/>
-    </row>
-    <row r="29" ht="21" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr"/>
+    </row>
+    <row r="30" ht="21" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>FAQ — Domanda</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>A&amp;A Biotechnology copre l'estrazione di RNA e microRNA?</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr"/>
-    </row>
-    <row r="30" ht="21" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr"/>
+    </row>
+    <row r="31" ht="21" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Sì, con kit dedicati a RNA totale e microRNA oltre a quelli per DNA genomico e plasmidico.</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr"/>
-    </row>
-    <row r="31" ht="21" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr"/>
+    </row>
+    <row r="32" ht="21" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>FAQ — Domanda</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>CABRU è distributore esclusivo di A&amp;A Biotechnology?</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr"/>
-    </row>
-    <row r="32" ht="21" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr"/>
+    </row>
+    <row r="33" ht="21" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>No. CABRU distribuisce A&amp;A Biotechnology in Italia senza esclusiva.</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr"/>
+      <c r="C33" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3057,7 +3083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3194,41 +3220,41 @@
       </c>
       <c r="C11" s="9" t="inlineStr"/>
     </row>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12" ht="51" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Il catalogo comprende reagenti per qPCR, PCR ed elettroforesi degli acidi nucleici, incluso Atlas ClearSight il sostituto atossico del bromuro di etidio (EtBr) per la colorazione del DNA, atossico e quindi sicuro nella manipolazione e nello smaltimento.</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
           <t>Voce elenco</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>DNA polimerasi della linea Atlas — Atlas Taq, Atlas HotTaq e Atlas Pfu, con i relativi buffer: 29 referenze a catalogo fanno riferimento alla chimica Taq. → Acidi nucleici</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13" ht="21" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr"/>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Voce elenco</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Mix pronti per PCR e qPCR e kit RT-qPCR: 21 referenze di mix, di cui 9 espressamente qPCR.</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr"/>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Voce elenco</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Coloranti del DNA Atlas ClearSight e ClearSight Gold , alternativa al bromuro di etidio nella colorazione dei gel.</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr"/>
@@ -3241,98 +3267,98 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
+          <t>Coloranti del DNA Atlas ClearSight e ClearSight Gold , alternativa al bromuro di etidio nella colorazione dei gel.</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Voce elenco</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
           <t>Elettroforesi — agarosi ultrapuri, tamponi pronti, loading dye e marcatori di peso molecolare. → Elettroforesi e western blot</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr"/>
-    </row>
-    <row r="16" ht="21" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Titolo sezione</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Titolo sezione</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>La compressa di agarosio: perché è il prodotto più riconoscibile</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr"/>
-    </row>
-    <row r="17" ht="81" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Testo</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr"/>
+    </row>
+    <row r="18" ht="81" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Bioatlas fornisce compresse che contengono in un unico pezzo agarosio, tampone e colorante del DNA. Chi prepara gel a mano sa che la pesata dell'agarosio e la manipolazione del colorante sono i due passaggi che generano variabilità e rifiuti da smaltire: la compressa li elimina entrambi. A catalogo CABRU figurano 6 referenze di compresse, nelle versioni semplice, ClearSight e ClearSight Gold.</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr"/>
-    </row>
-    <row r="18" ht="21" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Titolo sezione</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr"/>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Titolo sezione</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Aree di applicazione</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr"/>
-    </row>
-    <row r="19" ht="66" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Testo</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20" ht="66" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Amplificazione e rilevazione del DNA, PCR di routine e real-time, retrotrascrizione, visualizzazione su gel di agarosio e controllo dimensionale dei prodotti di amplificazione. Sono reagenti pensati per il carico di lavoro ordinario di un laboratorio di biologia molecolare, più che per una singola applicazione specialistica.</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr"/>
-    </row>
-    <row r="20" ht="21" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Titolo sezione</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Titolo sezione</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Come CABRU segue Bioatlas</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr"/>
-    </row>
-    <row r="21" ht="81" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Testo</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22" ht="81" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Bioatlas è il marchio da valutare quando l'obiettivo è ridurre il costo per reazione della PCR di routine senza cambiare protocollo, o quando si vuole togliere il bromuro di etidio dal laboratorio. CABRU verifica la corrispondenza fra il reagente in uso e l'equivalente Bioatlas, e su richiesta chiede al produttore i formati non presenti a catalogo. CABRU distribuisce Bioatlas in Italia in regime non esclusivo. → Richiedi informazioni e preventivo</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr"/>
-    </row>
-    <row r="22" ht="21" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Titolo sezione</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Domande frequenti</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr"/>
@@ -3340,132 +3366,145 @@
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
+          <t>Titolo sezione</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Domande frequenti</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr"/>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
           <t>FAQ — Domanda</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Chi distribuisce Bioatlas in Italia?</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr"/>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>CABRU distribuisce Bioatlas in Italia e ne gestisce richieste tecniche, preventivi e ordini come referente locale.</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr"/>
-    </row>
-    <row r="25" ht="21" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr"/>
+    </row>
+    <row r="26" ht="21" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>FAQ — Domanda</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Che cosa contiene una compressa di agarosio Bioatlas?</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr"/>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Agarosio, tampone e colorante del DNA in un unico pezzo, così da preparare il gel senza pesata dell'agarosio né manipolazione separata del colorante.</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr"/>
-    </row>
-    <row r="27" ht="21" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28" ht="21" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>FAQ — Domanda</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Il colorante ClearSight sostituisce il bromuro di etidio?</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr"/>
-    </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>È un colorante del DNA proposto come alternativa al bromuro di etidio nella colorazione dei gel. Restano valide le indicazioni di manipolazione e smaltimento del produttore.</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr"/>
-    </row>
-    <row r="29" ht="21" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr"/>
+    </row>
+    <row r="30" ht="21" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>FAQ — Domanda</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Bioatlas fornisce reagenti per qPCR?</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr"/>
-    </row>
-    <row r="30" ht="36" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Sì: nel catalogo CABRU figurano 9 referenze espressamente qPCR, oltre ai mix per PCR standard e alle polimerasi Atlas Taq, HotTaq e Pfu.</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr"/>
-    </row>
-    <row r="31" ht="21" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr"/>
+    </row>
+    <row r="32" ht="21" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>FAQ — Domanda</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>CABRU è distributore esclusivo di Bioatlas?</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr"/>
-    </row>
-    <row r="32" ht="21" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr"/>
+    </row>
+    <row r="33" ht="21" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>No. CABRU distribuisce Bioatlas in Italia senza esclusiva.</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr"/>
+      <c r="C33" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4434,7 +4473,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>CABRU — Reagenti e prodotti per laboratorio, industria e ricerca</t>
+          <t>CABRU — Offre prodotti per laboratori di ricerca in ambito scientifico</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr"/>
@@ -4447,7 +4486,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>CABRU s.a.s. distribuisce in Italia reagenti, kit, anticorpi, proteine e terreni di coltura per il laboratorio di ricerca e l'industria. Rappresentante di produttori internazionali selezionati.</t>
+          <t>CABRU — Reagenti e prodotti per laboratori di ricerca nell'ambito delle scienze della vita e per laboratori di controllo qualità di industrie biotecnologiche, farmaceutiche, alimentari, cosmetiche</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr"/>
@@ -4467,12 +4506,12 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Prodotti per laboratorio, industria e ricerca</t>
+          <t>CABRU — Offre prodotti per laboratori di ricerca in ambito scientifico</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr"/>
     </row>
-    <row r="8" ht="21" customHeight="1">
+    <row r="8" ht="51" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Titolo pagina</t>
@@ -4480,7 +4519,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Reagenti e soluzioni per la ricerca e l'industria.</t>
+          <t>CABRU — Reagenti e prodotti per laboratori di ricerca nell'ambito delle scienze della vita e per laboratori di controllo qualità di industrie biotecnologiche, farmaceutiche, alimentari, cosmetiche</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr"/>
@@ -4493,7 +4532,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>CABRU seleziona e distribuisce in Italia i prodotti di produttori internazionali specializzati: anticorpi, kit, proteine, reagenti per biologia molecolare e terreni di coltura, con un unico interlocutore.</t>
+          <t>CABRU seleziona e distribuisce in Italia anticorpi, molecole biochimiche, principi attivi, inibitori, proteine, kit, terreni, reagenti per biologia molecolare dei più affidabili produttori nazionali ed internazionali</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr"/>
@@ -4524,7 +4563,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr"/>
     </row>
-    <row r="12" ht="21" customHeight="1">
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Testo</t>
@@ -4532,7 +4571,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Una gamma completa per il laboratorio di ricerca e il controllo qualità.</t>
+          <t>Una gamma completa di prodotti per l'uso quotidiano nei laboratori di ricerca scientifica e di controllo qualità</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr"/>
@@ -4558,7 +4597,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Anticorpi primari mono e policlonali e anticorpi secondari.</t>
+          <t>Anticorpi primari mono e policlonali e anticorpi secondari marcati</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr"/>
@@ -4597,7 +4636,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Kit immunoenzimatici</t>
+          <t>KIT</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr"/>
@@ -4701,7 +4740,7 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Terreni per microbiologia</t>
+          <t>Terreni per microbiologia e biologia molecolare</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr"/>
@@ -4740,7 +4779,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Soluzioni pronte all'uso e polveri per la preparazione in laboratorio.</t>
+          <t>Soluzioni tampone e per le più svariate applicazioni pronte all'uso e polveri chimiche</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr"/>
@@ -4813,25 +4852,25 @@
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Prodotto in evidenza — Cayman Chemical</t>
+          <t>Prodotto in evidenza — Bioatlas</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Choline (chloride) — An essential nutrient with roles in liver, neurological and hematological function.</t>
+          <t>Atlas ClearSight Agarose Tablets 100 pcs — Compresse di agarosio con colorante per DNA incorporato: sostituto atossico dell'EtBr per l'elettroforesi su gel.</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr"/>
     </row>
-    <row r="35" ht="21" customHeight="1">
+    <row r="35" ht="36" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Prodotto in evidenza — FineTest</t>
+          <t>Prodotto in evidenza — Bioatlas</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>RRN3 antibody — Required for efficient transcription initiation by RNA polymerase I.</t>
+          <t>Titan HotTaq EvaGreen® qPCR Universal Mix 250 rxn — Master mix pronta all'uso per qPCR con rilevazione in EvaGreen® e Taq polimerasi hot-start.</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr"/>
@@ -4888,7 +4927,7 @@
       </c>
       <c r="C39" s="9" t="inlineStr"/>
     </row>
-    <row r="40" ht="36" customHeight="1">
+    <row r="40" ht="51" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Testo</t>
@@ -4896,7 +4935,7 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Distribuiamo in Italia i prodotti di 17 produttori internazionali specializzati. Ogni azienda copre un'area specifica delle scienze della vita.</t>
+          <t>Proponiamo in Italia eccellenti prodotti per ricerca scientifica, selezionati fra le più innovative ed affidabili aziende biotecnologiche in tutto il mondo per garantire ottime performance e riproducibilità nel tempo.</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr"/>
@@ -4927,7 +4966,7 @@
       </c>
       <c r="C42" s="9" t="inlineStr"/>
     </row>
-    <row r="43" ht="51" customHeight="1">
+    <row r="43" ht="81" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
           <t>Testo</t>
@@ -4935,7 +4974,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>CABRU s.a.s. seleziona produttori internazionali specializzati nelle scienze della vita e ne distribuisce i prodotti sul mercato italiano. Un solo referente per un'offerta che copre biologia molecolare, immunochimica, proteomica e microbiologia.</t>
+          <t>Proponiamo in Italia eccellenti prodotti per ricerca scientifica, selezionati per garantire ottime performance, riproducibilità nel tempo; accompagnamo la scelta e l'uso dei prodotti al fine di risolvere qualsiasi problematica dovesse sorgere; offriamo un servizio quanto più rapido ed efficiente possibile sia dal punto di vista tecnico-scientifico che commerciale. Garantiamo la catena del freddo.</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr"/>
@@ -4974,7 +5013,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Un unico punto di contatto per ordini, informazioni tecniche e assistenza.</t>
+          <t>Per informazioni o assistenza tecnico-scientifica o commerciale: info@cabru.it</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr"/>
@@ -4992,7 +5031,7 @@
       </c>
       <c r="C47" s="9" t="inlineStr"/>
     </row>
-    <row r="48" ht="36" customHeight="1">
+    <row r="48" ht="21" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
           <t>Testo</t>
@@ -5000,7 +5039,7 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Qualora il prodotto ricercato non compaia tra le categorie, CABRU ne verifica la disponibilità presso i produttori rappresentati e assiste il cliente dalla richiesta alla consegna.</t>
+          <t>Contattaci a info@cabru.it e faremo il possibile per soddisfare le tue esigenze</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr"/>
@@ -5182,7 +5221,7 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Per un preventivo, la disponibilità di un prodotto o un'informazione tecnica, CABRU è a disposizione e risponde nel più breve tempo possibile.</t>
+          <t>Per un preventivo, verificare la disponibilità di un prodotto o per un'informazione tecnica, CABRU è sempre a disposizione e risponde nel più breve tempo possibile.</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr"/>
@@ -5208,7 +5247,7 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>CABRU opera con un sistema di gestione della qualità certificato ISO 9001 e rappresenta produttori con sistemi qualità certificati (ISO 9001 e/o ISO 13485). Scopri di più sulla qualità .</t>
+          <t>CABRU opera con un sistema di gestione della qualità certificato ISO 9001 e rappresenta produttori con sistemi qualità certificati (ISO 9001 e/o ISO 13485).</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr"/>
@@ -5774,7 +5813,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Condalab, marchio di Conda S.A., produce terreni di coltura dal 1960 nel proprio stabilimento di Madrid ed esporta in oltre 130 Paesi. Dichiara più di 700 formulazioni di terreni disidratati e, cosa meno comune, produce anche gli ingredienti di base — agar, peptoni, agarosi — che entrano nei terreni. Fra le linee registrate figurano i terreni cromogenici CondaChrome®, i peptoni Condalow® e i kit qPCR Condagene®.</t>
+          <t>Condalab produce terreni di coltura dal 1960 nel proprio stabilimento di Madrid ed esporta in oltre 130 Paesi. Dichiara più di 700 formulazioni di terreni disidratati e, cosa meno comune, produce anche gli ingredienti di base — agar, peptoni, agarosi — che entrano nei terreni. Fra le linee registrate figurano i terreni cromogenici CondaChrome®, i peptoni Condalow® e i kit qPCR Condagene®.</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr"/>
@@ -5948,7 +5987,7 @@
       </c>
       <c r="C23" s="9" t="inlineStr"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="21" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
@@ -5956,7 +5995,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>CABRU distribuisce Condalab in Italia e ne gestisce richieste tecniche, preventivi e ordini come referente locale.</t>
+          <t>CABRU s.a.s. fornisce i prodotti Condalab gestendo richieste di preventivi, ordini e consegne.</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr"/>
@@ -10990,12 +11029,12 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Anticorpi primari, secondari e coniugati | CABRU</t>
+          <t>Anticorpi primari e secondari coniugati | CABRU</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="21" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>SEO — Meta description</t>
@@ -11003,7 +11042,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Anticorpi primari mono e policlonali, secondari e coniugati per la ricerca, dai produttori rappresentati da CABRU. Richiedi informazioni.</t>
+          <t>Anticorpi primari mono e policlonali, secondari coniugati per le più svariate applicazioni</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr"/>
@@ -11036,7 +11075,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Gli anticorpi per ricerca sono immunoglobuline selezionate per legare un antigene definito e renderlo rilevabile in una metodica di laboratorio: western blot, ELISA, immunoistochimica, immunofluorescenza, immunoprecipitazione, citofluorimetria e ChIP. Nel catalogo CABRU la categoria conta 21.314 referenze, prodotte da FineTest , ExBio , ReliaTech , Cayman Chemical , BioVendor , Affinity Biologicals e BioMedica Diagnostics .</t>
+          <t>Gli anticorpi per ricerca sono immunoglobuline selezionate per legare un antigene definito e renderlo rilevabile in una metodica di laboratorio: western blot, ELISA, immunoistochimica, immunofluorescenza, immunoprecipitazione, citofluorimetria e ChIP. Nel catalogo CABRU la categoria conta 21.314 referenze, prodotte da FineTest , Cayman Chemical , ExBio , ReliaTech , BioVendor , Affinity Biologicals , G Biosciences e BioMedica Diagnostics .</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr"/>
@@ -11171,7 +11210,7 @@
       </c>
       <c r="C18" s="9" t="inlineStr"/>
     </row>
-    <row r="19" ht="51" customHeight="1">
+    <row r="19" ht="36" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
@@ -11179,7 +11218,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>L'anticorpo primario riconosce direttamente l'antigene bersaglio; il secondario riconosce il primario ed è coniugato a un rivelatore (enzima o fluoroforo). Un approfondimento è disponibile nella guida dedicata.</t>
+          <t>L'anticorpo primario riconosce direttamente l'antigene bersaglio; il secondario riconosce il primario ed è coniugato a un rivelatore (enzima o fluoroforo).</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr"/>
@@ -11197,7 +11236,7 @@
       </c>
       <c r="C20" s="9" t="inlineStr"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="21" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
@@ -11205,7 +11244,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Sì, in particolare i monoclonali coniugati di ExBio. Il dettaglio è riportato nella pagina ExBio .</t>
+          <t>Sì, in particolare gli anticorpi prodotti da FineTest , ExBio e Cayman</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr"/>
@@ -11223,7 +11262,7 @@
       </c>
       <c r="C22" s="9" t="inlineStr"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="21" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
@@ -11231,7 +11270,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Sì: a partire dalla descrizione del target, CABRU ne verifica la disponibilità presso i produttori rappresentati.</t>
+          <t>Sì, si può valutare la fattibilità della richiesta</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr"/>
@@ -11252,7 +11291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11299,7 +11338,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Molecole biochimiche: inibitori, enzimi, standard | CABRU</t>
+          <t>Molecole biochimiche: principi attivi, inibitori, enzimi, standard | CABRU</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr"/>
@@ -11312,7 +11351,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Inibitori, attivatori, enzimi, substrati, coloranti, traccianti e standard analitici per la ricerca, dai produttori rappresentati da CABRU in Italia.</t>
+          <t>Principi attivi, inibitori, attivatori, enzimi, substrati, coloranti, traccianti e standard analitici.</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr"/>
@@ -11337,7 +11376,7 @@
       </c>
       <c r="C7" s="9" t="inlineStr"/>
     </row>
-    <row r="8" ht="96" customHeight="1">
+    <row r="8" ht="111" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Testo</t>
@@ -11345,7 +11384,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Le molecole biochimiche per la ricerca sono composti a basso peso molecolare usati come strumento sperimentale: inibitori e attivatori enzimatici, agonisti e antagonisti recettoriali, substrati, coloranti, traccianti, lipidi e standard analitici. La categoria è dominata da Cayman Chemical , presente in catalogo con 67.119 referenze che corrispondono a 23.429 prodotti distinti offerti in 265 tagli diversi; 63.952 di esse non sono anticorpi né kit, cioè sono molecole. Completa il quadro G Biosciences con reagenti e standard per proteomica e biologia molecolare.</t>
+          <t>Le molecole biochimiche per la ricerca sono composti a basso peso molecolare usati come strumento sperimentale: inibitori e attivatori enzimatici, agonisti e antagonisti recettoriali, substrati, coloranti, traccianti, lipidi e standard analitici. Cayman Chemical copre la maggior parte del paniere CABRU per questa tipologia di prodotti: è presente in catalogo con 67.119 referenze che corrispondono a 23.429 prodotti distinti offerti in 265 tagli diversi; 63.952 di esse non sono anticorpi né kit, cioè sono molecole. Completa il quadro G Biosciences con reagenti e standard per proteomica e biologia molecolare.</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr"/>
@@ -11363,93 +11402,93 @@
       </c>
       <c r="C9" s="9" t="inlineStr"/>
     </row>
-    <row r="10" ht="21" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Titolo sezione</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
+    <row r="10" ht="51" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Gli ambiti d'uso includono la somministrazione in vitro in colture cellulari o in vivo in cavie per studiarne gli effetti cellulari e sistemici oppure come riferimenti per analisi in cromatografia.</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr"/>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Titolo sezione</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Come si legge la potenza dichiarata</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11" ht="126" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Testo</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr"/>
+    </row>
+    <row r="12" ht="126" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Nel catalogo 29.392 descrizioni riportano un valore di IC 50 , K i o EC 50 . Sono numeri utili ma non trasferibili: l'IC 50 dipende dalle condizioni del saggio in cui è stato misurato — concentrazione di substrato, quantità di enzima, tempo di incubazione — e due valori ottenuti in laboratori diversi non sono confrontabili senza leggere il metodo. La K i è una costante di affinità e ha una portata più generale, ma resta legata al modello di inibizione assunto. Il criterio pratico è un altro: prima di scegliere un inibitore si guarda la selettività verso i bersagli vicini, perché un composto potente ma poco selettivo produce un fenotipo che non si riesce ad attribuire.</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12" ht="21" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Titolo sezione</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr"/>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Titolo sezione</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Solventi, formati e conservazione</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13" ht="126" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Testo</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr"/>
+    </row>
+    <row r="14" ht="126" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Molte referenze non sono polveri: eicosanoidi, lipidi e composti instabili sono forniti in soluzione in etanolo, metanolo o acetato di etile, e il solvente va considerato nel disegno dell'esperimento, perché non tutti si tollerano in coltura cellulare. Le soluzioni madre in DMSO vanno aliquotate: il DMSO è igroscopico e l'acqua assorbita fa precipitare il composto. I formati prevalenti sono i tagli in milligrammi — 5 mg su 11.974 referenze, 10 mg su 10.879, 1 mg su 10.702, 25 mg su 7.260 — accanto ai tagli da 500 µg (2.621) tipici degli standard analitici. La temperatura di conservazione e l'eventuale sensibilità a luce e ossigeno sono indicate in scheda tecnica; i lipidi polinsaturi si maneggiano riducendo l'esposizione all'aria.</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr"/>
-    </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Titolo sezione</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr"/>
+    </row>
+    <row r="15" ht="21" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Titolo sezione</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Dove approfondire e come cercare</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr"/>
-    </row>
-    <row r="15" ht="81" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Testo</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr"/>
+    </row>
+    <row r="16" ht="81" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Per le famiglie più richieste esistono pagine dedicate: la guida agli eicosanoidi , la guida agli endocannabinoidi e la pagina Tossicologia e scienze forensi , dove gli standard deuterati sono lo strumento di lavoro. Per individuare un composto bastano il nome o il numero CAS: la ricerca si fa nel catalogo prodotti , e per le molecole non presenti CABRU verifica la disponibilità presso i produttori rappresentati.</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr"/>
-    </row>
-    <row r="16" ht="21" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Titolo sezione</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Domande frequenti</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr"/>
@@ -11457,54 +11496,67 @@
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
+          <t>Titolo sezione</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Domande frequenti</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
           <t>FAQ — Domanda</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Quali standard analitici sono disponibili?</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr"/>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Standard di riferimento e traccianti per dosaggi e metodiche analitiche, dai produttori rappresentati; Cayman Chemical dispone di una gamma particolarmente estesa in quest'area.</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr"/>
-    </row>
-    <row r="19" ht="21" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>FAQ — Domanda</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>È possibile reperire una molecola specifica non a catalogo?</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr"/>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Sì: a partire dal nome o dal numero CAS, CABRU ne verifica la disponibilità presso i produttori rappresentati.</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr"/>
+      <c r="C21" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -11533,7 +11585,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Prodotti — Kit ELISA e saggi immunoenzimatici</t>
+          <t>Prodotti — Kit ELISA e saggi cellulari e biochimici</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11621,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Kit ELISA e saggi immunoenzimatici | CABRU</t>
+          <t>Kit ELISA e saggi cellulari e biochimici | CABRU</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr"/>
@@ -11582,7 +11634,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Kit ELISA ed EIA colorimetrici e fluorimetrici per il dosaggio di antigeni, metaboliti e biomarcatori, dai produttori rappresentati da CABRU in Italia.</t>
+          <t>Kit ELISA, EIA, colorimetrici e fluorimetrici per il dosaggio di antigeni, metaboliti e studio di vari processi biologici.</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr"/>
@@ -11602,12 +11654,12 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Kit ELISA e saggi immunoenzimatici</t>
+          <t>Kit ELISA e saggi cellulari e biochimici</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr"/>
     </row>
-    <row r="8" ht="81" customHeight="1">
+    <row r="8" ht="111" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Testo</t>
@@ -11615,7 +11667,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Un kit ELISA è un saggio immunoenzimatico su micropiastra che quantifica un analita confrontando il segnale del campione con una curva di calibrazione costruita su standard a concentrazione nota. Nel catalogo CABRU la categoria conta 12.602 referenze, di cui 12.327 nel formato a 96 pozzetti: le producono FineTest (11.579), Cayman Chemical (462), BioVendor (391), LDN (92) e Affinity Biologicals per l'area emostasi.</t>
+          <t>Un kit ELISA è un saggio immunoenzimatico su micropiastra che quantifica un analita confrontando il segnale del campione con una curva di calibrazione costruita su standard a concentrazione nota. Gli impieghi tipici comprendono la quantificazione di biomarcatori sierici, plasmatici, tissutali, surnatanti e terreni di coltura. Nel catalogo CABRU la categoria conta 12.602 referenze, di cui 12.327 nel formato a 96 pozzetti. CABRU fornisce i kit prodotti da Cayman Chemical (462), FineTest (11.579), LDN (92), Affinity Biologicals per l'area emostasi, G Biosciences e BioVendor (391).</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr"/>
@@ -11865,7 +11917,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Proteine ricombinanti e purificate, citochine e fattori di crescita per la ricerca, dai produttori rappresentati da CABRU in Italia. Richiedi informazioni.</t>
+          <t>Proteine ricombinanti, anche con tag, o purificate, citochine e fattori di crescita prodotti da FineTest, Cayman e ReliaTech. Richiedi informazioni.</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr"/>
@@ -11890,7 +11942,7 @@
       </c>
       <c r="C7" s="9" t="inlineStr"/>
     </row>
-    <row r="8" ht="126" customHeight="1">
+    <row r="8" ht="156" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Testo</t>
@@ -11898,7 +11950,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Le proteine per la ricerca sono molecole prodotte per via ricombinante o isolate da una fonte nativa, fornite come reagente per saggi funzionali, colture cellulari, studi di interazione e sviluppo di dosaggi: citochine, chemochine, fattori di crescita, enzimi, recettori solubili e proteine plasmatiche. Nel catalogo CABRU sono 10.312 le referenze la cui denominazione identifica una proteina, di cui 9.906 dichiarate ricombinanti: 7.308 di FineTest , 1.633 di ReliaTech , 1.017 di Cayman Chemical , 186 di G Biosciences e 106 di BioVendor . A queste si affiancano le 110 referenze di Enzyme Research Laboratories , dedicate a proteine ed enzimi della coagulazione, e la BSA di SEQENS nei formati da 100 g, 500 g e 1 kg.</t>
+          <t>Le proteine per la ricerca sono molecole prodotte per via ricombinante, anche con tag, o isolate e purificate da una fonte nativa, fornite come reagente per saggi funzionali, colture cellulari, studi di interazione, sviluppo di dosaggi e analisi cromatografiche: citochine, chemochine, fattori di crescita, enzimi, recettori solubili e proteine plasmatiche. Gli ambiti applicativi sono la biologia cellulare e la biochimica. Nel catalogo CABRU sono 10.312 le referenze la cui denominazione identifica una proteina, di cui 9.906 dichiarate ricombinanti: 7.308 di FineTest , 1.633 di ReliaTech (citochine e fattori di crescita), 1.017 di Cayman Chemical , 186 di G Biosciences e 106 di BioVendor . A queste si affiancano le 110 referenze di Enzyme Research Laboratories , dedicate a proteine ed enzimi della coagulazione, e la BSA di SEQENS nei formati da 100 g, 500 g e 1 kg.</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr"/>
@@ -12041,7 +12093,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Sì, in particolare tramite ReliaTech. Il dettaglio è riportato nella pagina ReliaTech .</t>
+          <t>Sì, in particolare si forniscono i prodotti FineTest , ReliaTech e Cayman</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr"/>
@@ -12316,7 +12368,7 @@
       </c>
       <c r="C18" s="9" t="inlineStr"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="21" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>FAQ — Risposta</t>
@@ -12324,7 +12376,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Sì, tra i reagenti Bioatlas per l'elettroforesi. Il dettaglio è riportato nella pagina Bioatlas .</t>
+          <t>Sì, Atlas ClearSight. Il dettaglio è riportato nella pagina Bioatlas .</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr"/>
@@ -12397,7 +12449,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="21" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>SEO — Meta description</t>
@@ -12405,7 +12457,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Reagenti e kit per elettroforesi di proteine 1D e 2D, western blot e marker di peso molecolare, dai produttori rappresentati da CABRU in Italia.</t>
+          <t>Reagenti e kit per elettroforesi di proteine 1D e 2D, western blot e marker di peso molecolare.</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr"/>
@@ -12438,7 +12490,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Elettroforesi delle proteine e western blot sono due passaggi consecutivi dello stesso flusso: la corsa separa le proteine di un estratto in base al peso molecolare o al punto isoelettrico, il blot le trasferisce su membrana e le rende accessibili a un anticorpo. I reagenti che servono a percorrerlo — tamponi di lisi, sistemi di dosaggio, matrici di separazione, coloranti, marker, membrane e bloccanti — provengono nel catalogo CABRU da G Biosciences , presente con 6.604 referenze complessive di cui 210 riconducibili a elettroforesi e blotting e 190 organizzate in kit.</t>
+          <t>Elettroforesi delle proteine e western blot sono due passaggi consecutivi dello stesso flusso: la corsa separa le proteine di un estratto in base al peso molecolare o al punto isoelettrico, il blot le trasferisce su membrana e le rende accessibili a un anticorpo. I reagenti che servono a percorrerlo — tamponi di lisi, sistemi di dosaggio, matrici di separazione, coloranti, marker, membrane e bloccanti — provengono nel catalogo CABRU da G Biosciences e FineTest : G Biosciences è presente con 6.604 referenze complessive, di cui 210 riconducibili a elettroforesi e blotting e 190 organizzate in kit.</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr"/>
@@ -12581,7 +12633,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Sì, tramite G Biosciences.</t>
+          <t>Sì</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr"/>

--- a/_tooling/CABRU_testi_IT_da_correggere.xlsx
+++ b/_tooling/CABRU_testi_IT_da_correggere.xlsx
@@ -4473,7 +4473,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>CABRU — Offre prodotti per laboratori di ricerca in ambito scientifico</t>
+          <t>CABRU Offre prodotti per laboratori di ricerca in ambito scientifico</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr"/>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C7" s="9" t="inlineStr"/>
     </row>
-    <row r="8" ht="51" customHeight="1">
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Titolo pagina</t>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>CABRU — Reagenti e prodotti per laboratori di ricerca nell'ambito delle scienze della vita e per laboratori di controllo qualità di industrie biotecnologiche, farmaceutiche, alimentari, cosmetiche</t>
+          <t>Reagenti e prodotti per laboratori di ricerca nell'ambito delle scienze della vita e per laboratori di controllo qualità di industrie biotecnologiche, farmaceutiche, alimentari, cosmetiche</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr"/>

--- a/_tooling/CABRU_testi_IT_da_correggere.xlsx
+++ b/_tooling/CABRU_testi_IT_da_correggere.xlsx
@@ -4478,7 +4478,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr"/>
     </row>
-    <row r="5" ht="51" customHeight="1">
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>SEO — Meta description</t>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>CABRU — Reagenti e prodotti per laboratori di ricerca nell'ambito delle scienze della vita e per laboratori di controllo qualità di industrie biotecnologiche, farmaceutiche, alimentari, cosmetiche</t>
+          <t>Reagenti e prodotti per laboratori di ricerca nell'ambito delle scienze della vita e per laboratori di controllo qualità di industrie biotecnologiche, farmaceutiche, alimentari, cosmetiche</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr"/>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>CABRU — Offre prodotti per laboratori di ricerca in ambito scientifico</t>
+          <t>CABRU Offre prodotti per laboratori di ricerca in ambito scientifico</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr"/>

--- a/_tooling/CABRU_testi_IT_da_correggere.xlsx
+++ b/_tooling/CABRU_testi_IT_da_correggere.xlsx
@@ -4426,7 +4426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5138,25 +5138,25 @@
     <row r="56" ht="21" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>Occhiello</t>
+          <t>Testo</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Dove trovarci</t>
+          <t>Un confronto prima dell'ordine evita la referenza sbagliata.</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr"/>
     </row>
-    <row r="57" ht="21" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>Titolo sezione</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t>Contatti</t>
+    <row r="57" ht="51" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Dicci l'applicazione, la matrice e il formato che ti servono: individuiamo la referenza adatta fra i produttori che rappresentiamo, verifichiamo disponibilità e tempi di consegna, e seguiamo la richiesta fino alla consegna con un unico referente.</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr"/>
@@ -5164,25 +5164,25 @@
     <row r="58" ht="21" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>Contatto</t>
+          <t>Occhiello</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Via Enrico Forlanini 52 20862 Arcore (MB)</t>
+          <t>Dove trovarci</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr"/>
     </row>
     <row r="59" ht="21" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>Contatto</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>039 6013988</t>
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>Titolo sezione</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>Contatti</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr"/>
@@ -5195,33 +5195,33 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
+          <t>Via Enrico Forlanini 52 20862 Arcore (MB)</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr"/>
+    </row>
+    <row r="61" ht="21" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Contatto</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>039 6013988</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr"/>
+    </row>
+    <row r="62" ht="21" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>Contatto</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
           <t>info@cabru.it</t>
-        </is>
-      </c>
-      <c r="C60" s="9" t="inlineStr"/>
-    </row>
-    <row r="61" ht="21" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>Sottotitolo</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t>Richieste di informazioni</t>
-        </is>
-      </c>
-      <c r="C61" s="9" t="inlineStr"/>
-    </row>
-    <row r="62" ht="36" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>Testo</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Per un preventivo, verificare la disponibilità di un prodotto o per un'informazione tecnica, CABRU è sempre a disposizione e risponde nel più breve tempo possibile.</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr"/>
@@ -5229,12 +5229,12 @@
     <row r="63" ht="21" customHeight="1">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>Titolo sezione</t>
+          <t>Sottotitolo</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Qualità certificata, dal produttore al laboratorio</t>
+          <t>Richieste di informazioni</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr"/>
@@ -5247,10 +5247,36 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
+          <t>Per un preventivo, verificare la disponibilità di un prodotto o per un'informazione tecnica, CABRU è sempre a disposizione e risponde nel più breve tempo possibile.</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr"/>
+    </row>
+    <row r="65" ht="21" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>Titolo sezione</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>Qualità certificata, dal produttore al laboratorio</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr"/>
+    </row>
+    <row r="66" ht="36" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
           <t>CABRU opera con un sistema di gestione della qualità certificato ISO 9001 e rappresenta produttori con sistemi qualità certificati (ISO 9001 e/o ISO 13485).</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr"/>
+      <c r="C66" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/_tooling/CABRU_testi_IT_da_correggere.xlsx
+++ b/_tooling/CABRU_testi_IT_da_correggere.xlsx
@@ -4574,7 +4574,7 @@
           <t>Una gamma completa di prodotti per l'uso quotidiano nei laboratori di ricerca scientifica e di controllo qualità</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr"/>
+      <c r="C12" s="9" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
